--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487939_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487939_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>P. PIEKUS</t>
+          <t>F. SANTANA ROSALES</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.9316</v>
+        <v>3.823</v>
       </c>
       <c r="E2" t="n">
-        <v>3.494</v>
+        <v>4.0563</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4376</v>
+        <v>-0.2333</v>
       </c>
       <c r="G2" t="n">
-        <v>1.2545</v>
+        <v>3.1362</v>
       </c>
       <c r="H2" t="n">
-        <v>1.4692</v>
+        <v>-0.55</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2147</v>
+        <v>3.6861</v>
       </c>
       <c r="J2" t="n">
-        <v>2.6058</v>
+        <v>3.8344</v>
       </c>
       <c r="K2" t="n">
-        <v>1.8613</v>
+        <v>0.3646</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7446</v>
+        <v>3.4698</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.3513</v>
+        <v>-0.6982</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.3921</v>
+        <v>-0.9145</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.9593</v>
+        <v>0.2164</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.2081</v>
+        <v>1.0406</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8325</v>
+        <v>1.0406</v>
       </c>
       <c r="S2" t="n">
-        <v>1.7106</v>
+        <v>-0.007</v>
       </c>
       <c r="T2" t="n">
-        <v>1.6988</v>
+        <v>0.222</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0118</v>
+        <v>-0.229</v>
       </c>
       <c r="V2" t="n">
-        <v>1.1746</v>
+        <v>-0.3467</v>
       </c>
       <c r="W2" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>0.9446</v>
+        <v>-0.3467</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>F. SANTANA ROSALES</t>
+          <t>P. FERNANDEZ CHOCARRO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.0165</v>
+        <v>2.7392</v>
       </c>
       <c r="E3" t="n">
-        <v>3.4553</v>
+        <v>2.8744</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.4388</v>
+        <v>-0.1352</v>
       </c>
       <c r="G3" t="n">
-        <v>3.1362</v>
+        <v>1.5308</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.55</v>
+        <v>-0.4883</v>
       </c>
       <c r="I3" t="n">
-        <v>3.6861</v>
+        <v>2.019</v>
       </c>
       <c r="J3" t="n">
-        <v>3.8344</v>
+        <v>2.6167</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3646</v>
+        <v>-0.431</v>
       </c>
       <c r="L3" t="n">
-        <v>3.4698</v>
+        <v>3.0477</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.6982</v>
+        <v>-1.086</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.9145</v>
+        <v>-0.0573</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2164</v>
+        <v>-1.0287</v>
       </c>
       <c r="P3" t="n">
-        <v>1.0406</v>
+        <v>2.0812</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.0406</v>
+        <v>2.0812</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.8136</v>
+        <v>-0.059</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3791</v>
+        <v>0.0277</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4345</v>
+        <v>-0.0867</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.3467</v>
+        <v>-0.8137</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.3467</v>
+        <v>-1.0437</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C. NKALOULOU MILANDOU</t>
+          <t>P. PIEKUS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6184</v>
+        <v>2.5371</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3401</v>
+        <v>2.4225</v>
       </c>
       <c r="F4" t="n">
-        <v>2.2784</v>
+        <v>0.1146</v>
       </c>
       <c r="G4" t="n">
-        <v>1.3786</v>
+        <v>1.2545</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9296</v>
+        <v>1.4692</v>
       </c>
       <c r="I4" t="n">
-        <v>0.449</v>
+        <v>-0.2147</v>
       </c>
       <c r="J4" t="n">
-        <v>2.0727</v>
+        <v>2.6058</v>
       </c>
       <c r="K4" t="n">
-        <v>1.4155</v>
+        <v>1.8613</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6572</v>
+        <v>0.7446</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.6941000000000001</v>
+        <v>-1.3513</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4859</v>
+        <v>-0.3921</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2082</v>
+        <v>-0.9593</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.8325</v>
+        <v>-0.2081</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.1218</v>
+        <v>-1.0406</v>
       </c>
       <c r="R4" t="n">
-        <v>2.2893</v>
+        <v>0.8325</v>
       </c>
       <c r="S4" t="n">
-        <v>1.86</v>
+        <v>0.3161</v>
       </c>
       <c r="T4" t="n">
-        <v>1.1769</v>
+        <v>0.6272</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6832</v>
+        <v>-0.3111</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2123</v>
+        <v>1.1746</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2123</v>
+        <v>0.23</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>0.9446</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. FERNANDEZ CHOCARRO</t>
+          <t>C. NKALOULOU MILANDOU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.3422</v>
+        <v>1.3082</v>
       </c>
       <c r="E5" t="n">
-        <v>2.5948</v>
+        <v>-0.5591</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2526</v>
+        <v>1.8673</v>
       </c>
       <c r="G5" t="n">
-        <v>1.5308</v>
+        <v>1.3786</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.4883</v>
+        <v>0.9296</v>
       </c>
       <c r="I5" t="n">
-        <v>2.019</v>
+        <v>0.449</v>
       </c>
       <c r="J5" t="n">
-        <v>2.6167</v>
+        <v>2.0727</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.431</v>
+        <v>1.4155</v>
       </c>
       <c r="L5" t="n">
-        <v>3.0477</v>
+        <v>0.6572</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.086</v>
+        <v>-0.6941000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0573</v>
+        <v>-0.4859</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.0287</v>
+        <v>-0.2082</v>
       </c>
       <c r="P5" t="n">
-        <v>2.0812</v>
+        <v>-0.8325</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-3.1218</v>
       </c>
       <c r="R5" t="n">
-        <v>2.0812</v>
+        <v>2.2893</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.456</v>
+        <v>0.5498</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2519</v>
+        <v>0.2777</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2042</v>
+        <v>0.2721</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.8137</v>
+        <v>0.2123</v>
       </c>
       <c r="W5" t="n">
-        <v>0.23</v>
+        <v>0.2123</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.0437</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.182</v>
+        <v>0.2407</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0.182</v>
+        <v>0.2407</v>
       </c>
       <c r="G6" t="n">
         <v>0.1429</v>
@@ -922,13 +922,13 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0391</v>
+        <v>0.0979</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0391</v>
+        <v>0.0979</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5324</v>
+        <v>-0.4736</v>
       </c>
       <c r="E7" t="n">
         <v>-0.7144</v>
       </c>
       <c r="F7" t="n">
-        <v>0.182</v>
+        <v>0.2407</v>
       </c>
       <c r="G7" t="n">
         <v>-0.5715</v>
@@ -1000,13 +1000,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0391</v>
+        <v>0.0979</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0391</v>
+        <v>0.0979</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. YARNOZ LUMBRERAS</t>
+          <t>P. ELSO GONZALEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.0597</v>
+        <v>-0.5918</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.138</v>
+        <v>-1.5864</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.9217</v>
+        <v>0.9945000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.2816</v>
+        <v>0.1134</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.1427</v>
+        <v>-1.4051</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.1389</v>
+        <v>1.5186</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.3424</v>
+        <v>-0.311</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3026</v>
+        <v>-1.6826</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.645</v>
+        <v>1.3716</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.9393</v>
+        <v>0.4244</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.4453</v>
+        <v>0.2775</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4939</v>
+        <v>0.147</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.2081</v>
+        <v>0.6244</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.0812</v>
+        <v>-1.0406</v>
       </c>
       <c r="R8" t="n">
-        <v>1.8731</v>
+        <v>1.6649</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4345</v>
+        <v>-0.3991</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0743</v>
+        <v>-0.2347</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5088</v>
+        <v>-0.1643</v>
       </c>
       <c r="V8" t="n">
-        <v>1.8645</v>
+        <v>-0.9305</v>
       </c>
       <c r="W8" t="n">
-        <v>2.2112</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.3467</v>
+        <v>-0.9305</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. ELSO GONZALEZ</t>
+          <t>P. YARNOZ LUMBRERAS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.4799</v>
+        <v>-1.0407</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.1221</v>
+        <v>-0.0309</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6422</v>
+        <v>-1.0098</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1134</v>
+        <v>-2.2816</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.4051</v>
+        <v>-1.1427</v>
       </c>
       <c r="I9" t="n">
-        <v>1.5186</v>
+        <v>-1.1389</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.311</v>
+        <v>-0.3424</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.6826</v>
+        <v>0.3026</v>
       </c>
       <c r="L9" t="n">
-        <v>1.3716</v>
+        <v>-0.645</v>
       </c>
       <c r="M9" t="n">
-        <v>0.4244</v>
+        <v>-1.9393</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2775</v>
+        <v>-1.4453</v>
       </c>
       <c r="O9" t="n">
-        <v>0.147</v>
+        <v>-0.4939</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6244</v>
+        <v>-0.2081</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0406</v>
+        <v>-2.0812</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6649</v>
+        <v>1.8731</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.2872</v>
+        <v>-0.4154</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7705</v>
+        <v>0.1815</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5167</v>
+        <v>-0.5969</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.9305</v>
+        <v>1.8645</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2.2112</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.9305</v>
+        <v>-0.3467</v>
       </c>
     </row>
     <row r="10">
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.1158</v>
+        <v>-3.8362</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.7604</v>
+        <v>-3.4808</v>
       </c>
       <c r="F10" t="n">
         <v>-0.3554</v>
@@ -1234,10 +1234,10 @@
         <v>1.8731</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4286</v>
+        <v>-0.1491</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0215</v>
+        <v>0.301</v>
       </c>
       <c r="U10" t="n">
         <v>-0.4501</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.326</v>
+        <v>-4.8221</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.4632</v>
+        <v>-2.1061</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.8627</v>
+        <v>-2.7159</v>
       </c>
       <c r="G11" t="n">
         <v>-2.3312</v>
@@ -1312,13 +1312,13 @@
         <v>1.2487</v>
       </c>
       <c r="S11" t="n">
-        <v>0.486</v>
+        <v>-0.0101</v>
       </c>
       <c r="T11" t="n">
-        <v>0.7111</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.225</v>
+        <v>-0.07829999999999999</v>
       </c>
       <c r="V11" t="n">
         <v>-2.6889</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. KNOTEK</t>
+          <t>A. CALVO TORRES</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.5084</v>
+        <v>-5.0355</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.4008</v>
+        <v>-5.19</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.1076</v>
+        <v>0.1545</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.406</v>
+        <v>-0.7608</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.0939</v>
+        <v>0.5414</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.3121</v>
+        <v>-1.3022</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.0464</v>
+        <v>0.0027</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.3712</v>
+        <v>0.313</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.6752</v>
+        <v>-0.3103</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.3596</v>
+        <v>-0.7635</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.7227</v>
+        <v>0.2284</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.6369</v>
+        <v>-0.9919</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.4162</v>
+        <v>-4.1624</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.0406</v>
+        <v>-6.2435</v>
       </c>
       <c r="R12" t="n">
-        <v>0.6244</v>
+        <v>2.0812</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1024</v>
+        <v>-1.0499</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3138</v>
+        <v>-0.3467</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2114</v>
+        <v>-0.7032</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.5838</v>
+        <v>0.9376</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.3975</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.5838</v>
+        <v>-0.4599</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. CALVO TORRES</t>
+          <t>J. KNOTEK</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.0269</v>
+        <v>-5.4805</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.0053</v>
+        <v>-3.0793</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.0216</v>
+        <v>-2.4012</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.7608</v>
+        <v>-4.406</v>
       </c>
       <c r="H13" t="n">
-        <v>0.5414</v>
+        <v>-2.0939</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.3022</v>
+        <v>-2.3121</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0027</v>
+        <v>-2.0464</v>
       </c>
       <c r="K13" t="n">
-        <v>0.313</v>
+        <v>-1.3712</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.3103</v>
+        <v>-0.6752</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.7635</v>
+        <v>-2.3596</v>
       </c>
       <c r="N13" t="n">
-        <v>0.2284</v>
+        <v>-0.7227</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.9919</v>
+        <v>-1.6369</v>
       </c>
       <c r="P13" t="n">
-        <v>-4.1624</v>
+        <v>-0.4162</v>
       </c>
       <c r="Q13" t="n">
-        <v>-6.2435</v>
+        <v>-1.0406</v>
       </c>
       <c r="R13" t="n">
-        <v>2.0812</v>
+        <v>0.6244</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.0414</v>
+        <v>-0.0745</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.162</v>
+        <v>0.0076</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.8794</v>
+        <v>-0.0822</v>
       </c>
       <c r="V13" t="n">
-        <v>0.9376</v>
+        <v>-0.5838</v>
       </c>
       <c r="W13" t="n">
-        <v>1.3975</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.4599</v>
+        <v>-0.5838</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-10.9584</v>
+        <v>-10.6322</v>
       </c>
       <c r="E14" t="n">
-        <v>-7.720000000000001</v>
+        <v>-7.3938</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.2382</v>
+        <v>-3.2385</v>
       </c>
       <c r="G14" t="n">
         <v>-4.4088</v>
@@ -1522,7 +1522,7 @@
         <v>5.8182</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.3864000000000002</v>
+        <v>-0.3864000000000003</v>
       </c>
       <c r="L14" t="n">
         <v>6.204599999999999</v>
@@ -1546,16 +1546,16 @@
         <v>15.609</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.4289</v>
+        <v>-1.1024</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8052999999999999</v>
+        <v>1.1314</v>
       </c>
       <c r="U14" t="n">
-        <v>-2.2341</v>
+        <v>-2.2339</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.998999999999999</v>
+        <v>-1.999</v>
       </c>
       <c r="W14" t="n">
         <v>4.387099999999999</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>F. BELLO MOURE</t>
+          <t>A. RODRIGUEZ AGUILAR</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.9941</v>
+        <v>6.5688</v>
       </c>
       <c r="E15" t="n">
-        <v>3.7088</v>
+        <v>2.1271</v>
       </c>
       <c r="F15" t="n">
-        <v>3.2853</v>
+        <v>4.4417</v>
       </c>
       <c r="G15" t="n">
-        <v>4.6647</v>
+        <v>0.466</v>
       </c>
       <c r="H15" t="n">
-        <v>2.4245</v>
+        <v>0.4865</v>
       </c>
       <c r="I15" t="n">
-        <v>2.2403</v>
+        <v>-0.0204</v>
       </c>
       <c r="J15" t="n">
-        <v>3.8117</v>
+        <v>0.9724</v>
       </c>
       <c r="K15" t="n">
-        <v>1.8613</v>
+        <v>0.4989</v>
       </c>
       <c r="L15" t="n">
-        <v>1.9504</v>
+        <v>0.4735</v>
       </c>
       <c r="M15" t="n">
-        <v>0.853</v>
+        <v>-0.5064</v>
       </c>
       <c r="N15" t="n">
-        <v>0.5632</v>
+        <v>-0.0124</v>
       </c>
       <c r="O15" t="n">
-        <v>0.2898</v>
+        <v>-0.4939</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.2081</v>
+        <v>3.3299</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.0812</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.8731</v>
+        <v>3.3299</v>
       </c>
       <c r="S15" t="n">
-        <v>2.3076</v>
+        <v>0.1902</v>
       </c>
       <c r="T15" t="n">
-        <v>1.7484</v>
+        <v>-0.0128</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5592</v>
+        <v>0.203</v>
       </c>
       <c r="V15" t="n">
-        <v>0.23</v>
+        <v>2.5827</v>
       </c>
       <c r="W15" t="n">
-        <v>0.23</v>
+        <v>1.1675</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.4152</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ AGUILAR</t>
+          <t>F. BELLO MOURE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.1997</v>
+        <v>6.0742</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4842</v>
+        <v>2.8516</v>
       </c>
       <c r="F16" t="n">
-        <v>3.7155</v>
+        <v>3.2227</v>
       </c>
       <c r="G16" t="n">
-        <v>0.466</v>
+        <v>4.6647</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4865</v>
+        <v>2.4245</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.0204</v>
+        <v>2.2403</v>
       </c>
       <c r="J16" t="n">
-        <v>0.9724</v>
+        <v>3.8117</v>
       </c>
       <c r="K16" t="n">
-        <v>0.4989</v>
+        <v>1.8613</v>
       </c>
       <c r="L16" t="n">
-        <v>0.4735</v>
+        <v>1.9504</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.5064</v>
+        <v>0.853</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0124</v>
+        <v>0.5632</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.4939</v>
+        <v>0.2898</v>
       </c>
       <c r="P16" t="n">
-        <v>3.3299</v>
+        <v>-0.2081</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-2.0812</v>
       </c>
       <c r="R16" t="n">
-        <v>3.3299</v>
+        <v>1.8731</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.1789</v>
+        <v>1.3877</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6556999999999999</v>
+        <v>0.8911</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5232</v>
+        <v>0.4965</v>
       </c>
       <c r="V16" t="n">
-        <v>2.5827</v>
+        <v>0.23</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1675</v>
+        <v>0.23</v>
       </c>
       <c r="X16" t="n">
-        <v>1.4152</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. NDIAYE</t>
+          <t>D. ROLLINS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.6796</v>
+        <v>3.392</v>
       </c>
       <c r="E17" t="n">
-        <v>2.3531</v>
+        <v>0.636</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3265</v>
+        <v>2.756</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1565</v>
+        <v>1.4838</v>
       </c>
       <c r="H17" t="n">
-        <v>1.2195</v>
+        <v>0.6739000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.063</v>
+        <v>0.8099</v>
       </c>
       <c r="J17" t="n">
-        <v>1.316</v>
+        <v>0.2959</v>
       </c>
       <c r="K17" t="n">
-        <v>1.2768</v>
+        <v>0.0576</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0392</v>
+        <v>0.2384</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.1595</v>
+        <v>1.1879</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.0573</v>
+        <v>0.6163999999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.1022</v>
+        <v>0.5715</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.2487</v>
+        <v>0.8325</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.0812</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0.8325</v>
       </c>
       <c r="S17" t="n">
-        <v>2.0205</v>
+        <v>0.3681</v>
       </c>
       <c r="T17" t="n">
-        <v>2.0746</v>
+        <v>0.3401</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0541</v>
+        <v>0.0281</v>
       </c>
       <c r="V17" t="n">
-        <v>1.7513</v>
+        <v>0.7076</v>
       </c>
       <c r="W17" t="n">
-        <v>1.0437</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>0.7076</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.5023</v>
+        <v>2.6682</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9311</v>
+        <v>1.0382</v>
       </c>
       <c r="F18" t="n">
-        <v>1.5712</v>
+        <v>1.63</v>
       </c>
       <c r="G18" t="n">
         <v>3.3267</v>
@@ -1858,13 +1858,13 @@
         <v>1.8731</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1944</v>
+        <v>0.3603</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.06850000000000001</v>
+        <v>0.0386</v>
       </c>
       <c r="U18" t="n">
-        <v>0.263</v>
+        <v>0.3217</v>
       </c>
       <c r="V18" t="n">
         <v>0.23</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. ROLLINS</t>
+          <t>A. OROZCO DOMINGUEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,40 +1891,40 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.4785</v>
+        <v>2.3705</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1002</v>
+        <v>1.8649</v>
       </c>
       <c r="F19" t="n">
-        <v>2.3783</v>
+        <v>0.5054999999999999</v>
       </c>
       <c r="G19" t="n">
-        <v>1.4838</v>
+        <v>0.8347</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6739000000000001</v>
+        <v>0.0044</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8099</v>
+        <v>0.8303</v>
       </c>
       <c r="J19" t="n">
-        <v>0.2959</v>
+        <v>1.1369</v>
       </c>
       <c r="K19" t="n">
         <v>0.0576</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2384</v>
+        <v>1.0793</v>
       </c>
       <c r="M19" t="n">
-        <v>1.1879</v>
+        <v>-0.3022</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6163999999999999</v>
+        <v>-0.0532</v>
       </c>
       <c r="O19" t="n">
-        <v>0.5715</v>
+        <v>-0.249</v>
       </c>
       <c r="P19" t="n">
         <v>0.8325</v>
@@ -1936,28 +1936,28 @@
         <v>0.8325</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5454</v>
+        <v>0.1195</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1957</v>
+        <v>0.1443</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3497</v>
+        <v>-0.0248</v>
       </c>
       <c r="V19" t="n">
-        <v>0.7076</v>
+        <v>0.5838</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.5838</v>
       </c>
       <c r="X19" t="n">
-        <v>0.7076</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. OROZCO DOMINGUEZ</t>
+          <t>S. NDIAYE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.7173</v>
+        <v>1.1755</v>
       </c>
       <c r="E20" t="n">
-        <v>1.3292</v>
+        <v>0.8529</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3881</v>
+        <v>0.3226</v>
       </c>
       <c r="G20" t="n">
-        <v>0.8347</v>
+        <v>0.1565</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0044</v>
+        <v>1.2195</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8303</v>
+        <v>-1.063</v>
       </c>
       <c r="J20" t="n">
-        <v>1.1369</v>
+        <v>1.316</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0576</v>
+        <v>1.2768</v>
       </c>
       <c r="L20" t="n">
-        <v>1.0793</v>
+        <v>0.0392</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.3022</v>
+        <v>-1.1595</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.0532</v>
+        <v>-0.0573</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.249</v>
+        <v>-1.1022</v>
       </c>
       <c r="P20" t="n">
-        <v>0.8325</v>
+        <v>-1.2487</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-2.0812</v>
       </c>
       <c r="R20" t="n">
         <v>0.8325</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5337</v>
+        <v>0.5164</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3915</v>
+        <v>0.5744</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1422</v>
+        <v>-0.058</v>
       </c>
       <c r="V20" t="n">
-        <v>0.5838</v>
+        <v>1.7513</v>
       </c>
       <c r="W20" t="n">
-        <v>0.5838</v>
+        <v>1.0437</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>0.7076</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2824</v>
+        <v>0.0454</v>
       </c>
       <c r="E21" t="n">
-        <v>0.6001</v>
+        <v>0.8145</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8826000000000001</v>
+        <v>-0.7691</v>
       </c>
       <c r="G21" t="n">
         <v>-0.1418</v>
@@ -2092,13 +2092,13 @@
         <v>2.2893</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5787</v>
+        <v>-0.2509</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.06850000000000001</v>
+        <v>0.1458</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5101</v>
+        <v>-0.3966</v>
       </c>
       <c r="V21" t="n">
         <v>0.23</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.3251</v>
+        <v>-0.598</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0169</v>
+        <v>0.6598000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.342</v>
+        <v>-1.2578</v>
       </c>
       <c r="G22" t="n">
         <v>-1.9847</v>
@@ -2170,13 +2170,13 @@
         <v>2.2893</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.1698</v>
+        <v>-0.4427</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.1091</v>
+        <v>-0.4662</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0606</v>
+        <v>0.0235</v>
       </c>
       <c r="V22" t="n">
         <v>-0.4599</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.3603</v>
+        <v>-1.9015</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.2633</v>
+        <v>-2.4776</v>
       </c>
       <c r="F23" t="n">
-        <v>0.903</v>
+        <v>0.5760999999999999</v>
       </c>
       <c r="G23" t="n">
         <v>-0.5506</v>
@@ -2248,13 +2248,13 @@
         <v>2.0812</v>
       </c>
       <c r="S23" t="n">
-        <v>1.6284</v>
+        <v>1.0873</v>
       </c>
       <c r="T23" t="n">
-        <v>0.7763</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>0.8521</v>
+        <v>0.5252</v>
       </c>
       <c r="V23" t="n">
         <v>-1.3975</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.341</v>
+        <v>-2.8475</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.565</v>
+        <v>-2.1008</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.776</v>
+        <v>-0.7466</v>
       </c>
       <c r="G24" t="n">
         <v>-0.8139999999999999</v>
@@ -2326,13 +2326,13 @@
         <v>1.2487</v>
       </c>
       <c r="S24" t="n">
-        <v>0.473</v>
+        <v>-0.0334</v>
       </c>
       <c r="T24" t="n">
-        <v>0.8416</v>
+        <v>0.3058</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3686</v>
+        <v>-0.3392</v>
       </c>
       <c r="V24" t="n">
         <v>-1.1675</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.3042</v>
+        <v>-4.5605</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.4569</v>
+        <v>-3.0283</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.8473</v>
+        <v>-1.5322</v>
       </c>
       <c r="G25" t="n">
         <v>-3.0323</v>
@@ -2404,13 +2404,13 @@
         <v>1.2487</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.1887</v>
+        <v>-0.4449</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.7177</v>
+        <v>-0.2891</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.471</v>
+        <v>-0.1559</v>
       </c>
       <c r="V25" t="n">
         <v>-1.2914</v>
@@ -2437,22 +2437,22 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>10.9585</v>
+        <v>12.3871</v>
       </c>
       <c r="E26" t="n">
-        <v>3.238400000000001</v>
+        <v>3.2383</v>
       </c>
       <c r="F26" t="n">
-        <v>7.720000000000002</v>
+        <v>9.148899999999999</v>
       </c>
       <c r="G26" t="n">
         <v>4.409000000000002</v>
       </c>
       <c r="H26" t="n">
-        <v>4.776400000000002</v>
+        <v>4.7764</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.3673999999999999</v>
+        <v>-0.3674000000000008</v>
       </c>
       <c r="J26" t="n">
         <v>10.2273</v>
@@ -2461,13 +2461,13 @@
         <v>4.3901</v>
       </c>
       <c r="L26" t="n">
-        <v>5.837299999999999</v>
+        <v>5.837300000000001</v>
       </c>
       <c r="M26" t="n">
         <v>-5.818399999999999</v>
       </c>
       <c r="N26" t="n">
-        <v>0.3864</v>
+        <v>0.3863999999999999</v>
       </c>
       <c r="O26" t="n">
         <v>-6.2047</v>
@@ -2482,19 +2482,19 @@
         <v>18.7308</v>
       </c>
       <c r="S26" t="n">
-        <v>1.4287</v>
+        <v>2.8576</v>
       </c>
       <c r="T26" t="n">
-        <v>2.2342</v>
+        <v>2.234</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.8051999999999999</v>
+        <v>0.6235000000000003</v>
       </c>
       <c r="V26" t="n">
-        <v>1.9991</v>
+        <v>1.999100000000001</v>
       </c>
       <c r="W26" t="n">
-        <v>6.386000000000001</v>
+        <v>6.386</v>
       </c>
       <c r="X26" t="n">
         <v>-4.3871</v>
